--- a/Data & Code/template_tb.xlsx
+++ b/Data & Code/template_tb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Downloads\Skripsi\Data &amp; Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DB309C-7B1E-41E7-9F86-8F1EFB42F60A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{646720A6-8CC4-4444-AD87-68B927CEFEF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
